--- a/output/pdf_financials_xlsx/PRIZ.xlsx
+++ b/output/pdf_financials_xlsx/PRIZ.xlsx
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.132792</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.007184</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1.2675</v>
+        <v>1.400292</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.134273</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.183845</v>
+        <v>0.051053</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.09167699999999999</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">

--- a/output/pdf_financials_xlsx/PRIZ.xlsx
+++ b/output/pdf_financials_xlsx/PRIZ.xlsx
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.339263</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>1.705589</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.153513</v>
       </c>
     </row>
     <row r="116">
@@ -3712,7 +3712,11 @@
           <t>Proceeds from sale of marketable securities (Note 4)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -3774,7 +3778,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>0.5</v>
       </c>
@@ -4336,7 +4344,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>0.339263</v>
       </c>
